--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -637,27 +637,31 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -748,27 +756,31 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -859,27 +875,31 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -970,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1086,19 +1118,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1165,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1306,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1308,19 +1344,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 48分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -1331,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1360,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1381,7 +1417,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1425,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1442,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1492,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1528,915 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1113,27 +1113,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1190,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1228,27 +1232,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1280,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1339,27 +1351,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1367,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1450,27 +1470,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1478,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1502,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1561,27 +1589,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1589,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1613,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1677,19 +1713,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
@@ -1700,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1724,33 +1760,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1788,19 +1828,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -1811,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1835,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1855,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1980,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2080,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2095,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2316,12 +2356,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2431,12 +2471,702 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1718,17 +1718,21 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1823,12 +1827,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1840,10 +1844,14 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1851,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1905,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1943,19 +1951,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -1966,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1990,37 +1998,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2307,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2361,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2652,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2882,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2931,7 +2939,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2997,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3046,7 +3054,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3059,22 +3067,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3126,45 +3134,160 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="AC23" s="2" t="inlineStr">
+      <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>2/11</t>
         </is>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1956,17 +1956,21 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,12 +2002,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2023,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2061,27 +2065,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2133,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2176,27 +2184,31 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2204,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2287,27 +2303,31 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2315,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,37 +2359,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2402,27 +2422,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2430,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,37 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2517,27 +2541,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2545,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2637,19 +2665,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 22分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -2660,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,17 +2712,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2704,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2775,31 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2775,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,37 +2831,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3005,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3120,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3169,7 +3201,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3182,22 +3214,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3230,12 +3262,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3249,47 +3281,852 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>2/11</t>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2660,27 +2660,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2727,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2780,24 +2784,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2894,27 +2898,31 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2922,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2954,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2966,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3009,27 +3017,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3037,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3061,17 +3073,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3081,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3124,27 +3136,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3152,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3196,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3255,31 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3267,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,37 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3354,27 +3374,31 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3382,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3406,27 +3430,27 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3474,19 +3498,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 30分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
@@ -3497,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3521,17 +3545,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3541,17 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3584,27 +3608,31 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3612,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,37 +3664,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3732,26 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>10:21采样：该车到重点站德川路华夏东路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3727,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,17 +3783,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3771,12 +3803,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3842,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3896,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,17 +4148,592 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
           <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>72.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>72.7</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>72.7</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3260,24 +3260,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,27 +3493,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 30分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,12 +3549,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3560,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3613,24 +3617,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3727,24 +3731,24 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站德川路华夏东路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,12 +3787,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,27 +3850,31 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -3874,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,17 +3906,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3918,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3961,27 +3969,31 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3989,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4013,17 +4025,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4033,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4076,27 +4088,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4104,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4128,32 +4144,32 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4334,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4383,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4514,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4739,477 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>2/11</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3855,24 +3855,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4207,27 +4207,31 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4235,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4263,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4279,12 +4283,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,27 +4326,31 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4350,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4382,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4394,17 +4402,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4437,27 +4445,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4465,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4501,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4509,17 +4521,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4552,27 +4564,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4580,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,37 +4620,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4667,27 +4683,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4695,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4739,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4994,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5219,481 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>9/11</t>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4450,24 +4450,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4569,24 +4569,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4688,24 +4688,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4802,27 +4802,31 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4858,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4874,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4917,27 +4921,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4945,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,17 +4977,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4989,17 +4997,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5032,27 +5040,31 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5060,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,32 +5096,32 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5147,27 +5159,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5175,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5215,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5219,12 +5235,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5470,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5699,493 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>68分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>3/11</t>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,27 +5278,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5334,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5350,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5393,27 +5397,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5421,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,32 +5453,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5633,14 +5641,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>13:41采样：该车到重点站唐陆公路川桥路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5655,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5684,7 +5692,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5704,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6012,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6183,251 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>7/11</t>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5283,24 +5283,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5402,24 +5402,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5516,27 +5516,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5544,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5572,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5588,12 +5592,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5631,29 +5635,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13:41采样：该车到重点站唐陆公路川桥路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5663,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5691,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5712,12 +5716,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5755,26 +5759,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,22 +5806,22 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5874,26 +5874,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 52分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5901,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5921,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5945,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,7 +6303,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,17 +6413,255 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5754,27 +5754,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5810,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5826,12 +5830,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5869,27 +5873,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 52分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5897,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,32 +5929,32 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5984,7 +5992,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -6001,12 +6009,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6048,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6055,22 +6063,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6103,29 +6111,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6135,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6167,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6184,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6222,29 +6230,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,12 +6286,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6293,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6346,19 +6354,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 46分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
@@ -6369,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6398,7 +6406,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6461,19 +6469,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站佳林路金高路 ETA 51分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,7 +6525,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6537,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6659,612 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>1/11</t>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,17 +5587,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5997,24 +5997,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6235,24 +6235,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -6359,17 +6359,21 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,32 +6405,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6464,29 +6468,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站佳林路金高路 ETA 51分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6524,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6535,22 +6539,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6583,29 +6587,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,12 +6643,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6664,12 +6668,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6702,29 +6706,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,12 +6762,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6773,12 +6777,12 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6788,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6821,29 +6825,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6853,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,12 +6881,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6902,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6961,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车17:20，减去该车自身同类时段历史终点停站中位数14分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6972,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,7 +7005,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7011,22 +7015,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7064,19 +7068,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站唐陆公路龙东大道 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,7 +7124,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7140,12 +7144,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7183,19 +7187,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站唐陆公路龙东大道 ETA 38分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7210,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,32 +7243,742 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
         <is>
           <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,22 +5587,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,22 +6063,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6592,24 +6592,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6830,24 +6830,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,22 +6896,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6944,29 +6944,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车17:20，减去该车自身同类时段历史终点停站中位数14分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7068,26 +7068,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路龙东大道 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7095,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,7 +7120,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7134,17 +7130,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7182,29 +7178,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路龙东大道 ETA 38分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7214,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,12 +7234,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7263,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7306,19 +7302,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 30分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -7329,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,32 +7349,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7433,7 +7429,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车18:05，减去该车自身同类时段历史终点停站中位数14分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7448,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,7 +7473,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7487,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7535,29 +7531,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7567,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,12 +7587,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7616,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7659,19 +7655,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7686,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7715,7 +7711,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7735,7 +7731,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7778,19 +7774,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7805,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,7 +7830,7 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7854,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7897,19 +7893,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7924,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7953,32 +7949,746 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>8/11</t>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,17 +6539,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7068,19 +7068,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 18分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:31采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7302,19 +7302,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 30分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:31采样，终点ETA 19分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7536,24 +7536,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,17 +7602,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7655,19 +7655,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站唐陆公路顾家浜路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7774,19 +7774,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站唐陆公路唐龙路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7893,19 +7893,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站荷泽路长岛路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8012,19 +8012,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+          <t>17:31采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8692,6 +8692,125 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,17 +6658,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,22 +7015,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7302,19 +7302,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:31采样，终点ETA 19分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 1分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7412,24 +7412,24 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车18:05，减去该车自身同类时段历史终点停站中位数14分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站唐陆公路顾家浜路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站唐陆公路唐龙路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7888,29 +7888,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站荷泽路长岛路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8007,29 +8007,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8131,24 +8131,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±9分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8250,26 +8250,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 52分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8277,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,32 +8297,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8349,7 +8345,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8369,24 +8365,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±11分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8396,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8415,17 +8411,17 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8435,17 +8431,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8488,7 +8484,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -8500,7 +8496,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8515,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,7 +8540,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8564,7 +8560,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8607,24 +8603,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站德川路华夏东路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8634,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,7 +8659,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8683,7 +8679,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8696,24 +8692,24 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8726,34 +8722,34 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,47 +8763,642 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
           <t>18:40</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="W71" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>74.6</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,17 +4754,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,17 +6063,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8012,24 +8012,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8126,29 +8126,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8250,19 +8250,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 52分钟</t>
+          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 34分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8365,19 +8365,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±9分钟</t>
+          <t>18:41采样：该车到重点站唐陆公路创新路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8484,19 +8484,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>18:41采样：该车到重点站唐陆公路春雅路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8603,26 +8603,22 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站德川路华夏东路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 48分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8630,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,32 +8650,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8722,24 +8718,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±6分钟</t>
+          <t>18:41采样：该车到重点站东陆路金海路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8749,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8778,7 +8774,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8798,12 +8794,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8987,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,12 +9032,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9155,12 +9151,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,12 +9265,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9344,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9393,12 +9389,131 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,17 +5587,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,17 +6420,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,17 +6539,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,17 +7015,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,17 +7602,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,17 +7959,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8131,24 +8131,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8245,27 +8245,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8273,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,12 +8301,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8322,7 +8326,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8360,29 +8364,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>18:41采样：该车到重点站唐陆公路创新路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,12 +8420,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8441,7 +8445,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8479,29 +8483,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>18:41采样：该车到重点站唐陆公路春雅路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8511,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,12 +8539,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8550,17 +8554,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8598,27 +8602,31 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8626,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8658,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8670,17 +8678,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8718,26 +8726,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>18:41采样：该车到重点站东陆路金海路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8745,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,12 +8773,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8794,12 +8798,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8832,29 +8836,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8864,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8892,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8903,17 +8907,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8956,24 +8960,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,7 +9016,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9032,7 +9036,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9087,7 +9091,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车20:30，减去该车自身同类时段历史终点停站中位数13分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9102,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,7 +9135,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9141,17 +9145,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9194,19 +9198,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9221,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9250,7 +9254,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9270,7 +9274,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9389,7 +9393,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9459,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9503,17 +9507,374 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>73.7</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>5/11</t>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,14 +7483,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,17 +8435,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8554,14 +8554,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8721,27 +8721,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8749,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,12 +8777,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8798,7 +8802,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8841,12 +8845,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -8868,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8917,12 +8921,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8955,29 +8959,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8987,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,12 +9015,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9036,7 +9040,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9074,29 +9078,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车20:30，减去该车自身同类时段历史终点停站中位数13分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9106,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,12 +9134,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9155,7 +9159,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9193,12 +9197,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -9210,12 +9214,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9225,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,12 +9253,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9312,29 +9316,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9344,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9368,12 +9372,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9383,17 +9387,17 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9431,29 +9435,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9463,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,12 +9491,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9512,12 +9516,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9560,21 +9564,17 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,29 +9606,29 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9674,24 +9674,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9869,12 +9869,250 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>22:27</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9321,24 +9321,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,27 +9554,31 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9582,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9610,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9626,12 +9630,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9669,29 +9673,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9701,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,12 +9729,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9750,12 +9754,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9788,29 +9792,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9820,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,12 +9848,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9869,12 +9873,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9916,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -9924,14 +9928,10 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 51分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,17 +9963,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10031,19 +10031,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">

--- a/data/export/2026-09-19-182路.xlsx
+++ b/data/export/2026-09-19-182路.xlsx
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,27 +9911,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 51分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9939,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,17 +9967,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9983,12 +9987,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10026,29 +10030,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>64分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10058,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,12 +10086,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10107,12 +10111,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
